--- a/J1리그_2026-2027.xlsx
+++ b/J1리그_2026-2027.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,11 +560,19 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -577,47 +585,47 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -654,16 +662,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
           <t>우라와</t>
@@ -671,47 +687,47 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0/0.5</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -748,14 +764,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -765,47 +789,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -842,14 +866,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,47 +891,47 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -936,14 +968,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -953,47 +993,47 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0/0.5</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -1030,14 +1070,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1047,47 +1095,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1172,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1141,47 +1197,47 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0/0.5</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1274,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1235,47 +1299,47 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.5/3</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1376,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1329,47 +1401,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0/-0.5</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -1406,64 +1478,1012 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>교토</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08.14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>베르디</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>가시와</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>가시마</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>나고야</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>미토</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>감바 오사카</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>시미즈</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>요코하마 M.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>오카야마</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>V-바렌 나가사키</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>가와사키</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>교토</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>우라와</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>산프레체 히로시마</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>고베</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>FC 도쿄</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>아비스파 후쿠오카</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>세레소 오사카</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>J1리그</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>지바</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>교토</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>마치다</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
